--- a/Vulnerability Test Results/findings.xlsx
+++ b/Vulnerability Test Results/findings.xlsx
@@ -537,11 +537,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -559,11 +555,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -597,11 +589,7 @@
           <t>Flask</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
